--- a/files/excel-mastery-1-2.xlsx
+++ b/files/excel-mastery-1-2.xlsx
@@ -541,7 +541,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -549,8 +549,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -647,9 +650,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -704,21 +704,12 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -731,29 +722,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
@@ -869,246 +839,290 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="25" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="25" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準 2" xfId="2"/>
+    <cellStyle name="パーセント" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -1548,14 +1562,14 @@
   <dimension ref="B2:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col width="2.36328125" customWidth="1" style="158" min="1" max="3"/>
-    <col width="26" customWidth="1" style="158" min="4" max="4"/>
-    <col width="14.08984375" customWidth="1" style="158" min="5" max="9"/>
-    <col width="12" customWidth="1" style="158" min="10" max="10"/>
-    <col width="28" customWidth="1" style="158" min="11" max="11"/>
+    <col width="2.36328125" customWidth="1" min="1" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="14.08984375" customWidth="1" min="5" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.5" customHeight="1" s="158">
+    <row r="2" ht="19.5" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>1-2. 操作が速い ― キーボード操作と数式展開のイメージ</t>
@@ -1563,7 +1577,7 @@
       </c>
       <c r="C2" s="1" t="n"/>
     </row>
-    <row r="5" ht="13.5" customHeight="1" s="158">
+    <row r="5" ht="13.5" customHeight="1">
       <c r="D5" s="16" t="inlineStr">
         <is>
           <t>① キーボードでセル間・表間を高速移動する</t>
@@ -1575,27 +1589,27 @@
       <c r="H5" s="16" t="n"/>
       <c r="I5" s="16" t="n"/>
     </row>
-    <row r="7" ht="13.5" customHeight="1" s="158">
+    <row r="7" ht="13.5" customHeight="1">
       <c r="D7" s="6" t="inlineStr">
         <is>
           <t>操作イメージ</t>
         </is>
       </c>
-      <c r="E7" s="34" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>キー</t>
         </is>
       </c>
-      <c r="F7" s="34" t="n"/>
-      <c r="G7" s="34" t="inlineStr">
+      <c r="F7" s="33" t="n"/>
+      <c r="G7" s="33" t="inlineStr">
         <is>
           <t>効果</t>
         </is>
       </c>
-      <c r="H7" s="34" t="n"/>
-      <c r="I7" s="34" t="n"/>
-    </row>
-    <row r="8" ht="13.5" customHeight="1" s="158">
+      <c r="H7" s="33" t="n"/>
+      <c r="I7" s="33" t="n"/>
+    </row>
+    <row r="8" ht="13.5" customHeight="1">
       <c r="D8" s="10" t="inlineStr">
         <is>
           <t>表の端まで一気に移動</t>
@@ -1615,7 +1629,7 @@
       <c r="H8" s="10" t="n"/>
       <c r="I8" s="10" t="n"/>
     </row>
-    <row r="9" ht="13.5" customHeight="1" s="158">
+    <row r="9" ht="13.5" customHeight="1">
       <c r="D9" s="11" t="inlineStr">
         <is>
           <t>端まで一括で範囲選択</t>
@@ -1635,7 +1649,7 @@
       <c r="H9" s="11" t="n"/>
       <c r="I9" s="11" t="n"/>
     </row>
-    <row r="10" ht="13.5" customHeight="1" s="158">
+    <row r="10" ht="13.5" customHeight="1">
       <c r="D10" s="11" t="inlineStr">
         <is>
           <t>シートを切り替える</t>
@@ -1655,7 +1669,7 @@
       <c r="H10" s="11" t="n"/>
       <c r="I10" s="11" t="n"/>
     </row>
-    <row r="11" ht="13.5" customHeight="1" s="158">
+    <row r="11" ht="13.5" customHeight="1">
       <c r="D11" s="12" t="inlineStr">
         <is>
           <t>セルを編集モードに</t>
@@ -1682,63 +1696,63 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="13.5" customHeight="1" s="158">
+    <row r="14" ht="13.5" customHeight="1">
       <c r="D14" s="6" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="E14" s="42" t="inlineStr">
+      <c r="E14" s="41" t="inlineStr">
         <is>
           <t>売上(円)</t>
         </is>
       </c>
-      <c r="F14" s="35" t="n"/>
-      <c r="G14" s="35" t="n"/>
-      <c r="H14" s="35" t="n"/>
-      <c r="I14" s="35" t="n"/>
-    </row>
-    <row r="15" ht="13.5" customHeight="1" s="158">
-      <c r="D15" s="36" t="inlineStr">
+      <c r="F14" s="34" t="n"/>
+      <c r="G14" s="34" t="n"/>
+      <c r="H14" s="34" t="n"/>
+      <c r="I14" s="34" t="n"/>
+    </row>
+    <row r="15" ht="13.5" customHeight="1">
+      <c r="D15" s="35" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="E15" s="37" t="n">
+      <c r="E15" s="36" t="n">
         <v>7072000</v>
       </c>
     </row>
-    <row r="16" ht="13.5" customHeight="1" s="158">
-      <c r="D16" s="38" t="inlineStr">
+    <row r="16" ht="13.5" customHeight="1">
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="E16" s="39" t="n">
+      <c r="E16" s="38" t="n">
         <v>8130000</v>
       </c>
     </row>
-    <row r="17" ht="13.5" customHeight="1" s="158">
-      <c r="D17" s="38" t="inlineStr">
+    <row r="17" ht="13.5" customHeight="1">
+      <c r="D17" s="37" t="inlineStr">
         <is>
           <t>9月</t>
         </is>
       </c>
-      <c r="E17" s="39" t="n">
+      <c r="E17" s="38" t="n">
         <v>6540000</v>
       </c>
     </row>
-    <row r="18" ht="13.5" customHeight="1" s="158">
-      <c r="D18" s="40" t="inlineStr">
+    <row r="18" ht="13.5" customHeight="1">
+      <c r="D18" s="39" t="inlineStr">
         <is>
           <t>10月</t>
         </is>
       </c>
-      <c r="E18" s="41" t="n">
+      <c r="E18" s="40" t="n">
         <v>5980000</v>
       </c>
     </row>
-    <row r="19" ht="13.5" customHeight="1" s="158">
+    <row r="19" ht="13.5" customHeight="1">
       <c r="D19" s="24" t="inlineStr">
         <is>
           <t>合計</t>
@@ -1749,7 +1763,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="13.5" customHeight="1" s="158">
+    <row r="23" ht="13.5" customHeight="1">
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="16" t="inlineStr">
         <is>
@@ -1769,7 +1783,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="13.5" customHeight="1" s="158">
+    <row r="26" ht="13.5" customHeight="1">
       <c r="D26" s="6" t="inlineStr">
         <is>
           <t>商品</t>
@@ -1791,16 +1805,16 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="13.5" customHeight="1" s="158">
+    <row r="27" ht="13.5" customHeight="1">
       <c r="D27" s="10" t="inlineStr">
         <is>
           <t>シングル</t>
         </is>
       </c>
-      <c r="E27" s="44" t="n">
+      <c r="E27" s="43" t="n">
         <v>12000</v>
       </c>
-      <c r="F27" s="45" t="n">
+      <c r="F27" s="44" t="n">
         <v>30</v>
       </c>
       <c r="G27" s="13">
@@ -1808,45 +1822,45 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="13.5" customHeight="1" s="158">
+    <row r="28" ht="13.5" customHeight="1">
       <c r="D28" s="11" t="inlineStr">
         <is>
           <t>ツイン</t>
         </is>
       </c>
-      <c r="E28" s="46" t="n">
+      <c r="E28" s="45" t="n">
         <v>18000</v>
       </c>
-      <c r="F28" s="47" t="n">
+      <c r="F28" s="46" t="n">
         <v>22</v>
       </c>
-      <c r="G28" s="39">
+      <c r="G28" s="38">
         <f>E28*F28</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="13.5" customHeight="1" s="158">
+    <row r="29" ht="13.5" customHeight="1">
       <c r="D29" s="12" t="inlineStr">
         <is>
           <t>スイート</t>
         </is>
       </c>
-      <c r="E29" s="48" t="n">
+      <c r="E29" s="47" t="n">
         <v>52000</v>
       </c>
-      <c r="F29" s="49" t="n">
+      <c r="F29" s="48" t="n">
         <v>8</v>
       </c>
-      <c r="G29" s="41">
+      <c r="G29" s="40">
         <f>E29*F29</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="13.5" customHeight="1" s="158">
-      <c r="D30" s="122" t="n"/>
-      <c r="E30" s="122" t="n"/>
-      <c r="F30" s="122" t="n"/>
-      <c r="G30" s="122" t="n"/>
+    <row r="30" ht="13.5" customHeight="1">
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="D31" s="3" t="inlineStr">
@@ -1862,7 +1876,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="13.5" customHeight="1" s="158">
+    <row r="35" ht="13.5" customHeight="1">
       <c r="D35" s="16" t="inlineStr">
         <is>
           <t>③ 絶対/相対/複合参照を使い分ける（$の位置）</t>
@@ -1885,126 +1899,126 @@
       </c>
       <c r="E37" s="4" t="n"/>
     </row>
-    <row r="38" ht="13.5" customHeight="1" s="158">
+    <row r="38" ht="13.5" customHeight="1">
       <c r="D38" s="26" t="inlineStr">
         <is>
           <t>数量＼単価</t>
         </is>
       </c>
-      <c r="E38" s="59" t="n">
+      <c r="E38" s="55" t="n">
         <v>10000</v>
       </c>
-      <c r="F38" s="59" t="n">
+      <c r="F38" s="55" t="n">
         <v>20000</v>
       </c>
-      <c r="G38" s="59" t="n">
+      <c r="G38" s="55" t="n">
         <v>30000</v>
       </c>
-      <c r="H38" s="59" t="n">
+      <c r="H38" s="55" t="n">
         <v>50000</v>
       </c>
     </row>
-    <row r="39" ht="13.5" customHeight="1" s="158">
-      <c r="D39" s="45" t="n">
+    <row r="39" ht="13.5" customHeight="1">
+      <c r="D39" s="44" t="n">
         <v>1</v>
       </c>
       <c r="E39" s="13">
         <f>$D39*E$38</f>
         <v/>
       </c>
-      <c r="F39" s="54">
+      <c r="F39" s="52">
         <f>$D39*F$38</f>
         <v/>
       </c>
-      <c r="G39" s="54">
+      <c r="G39" s="52">
         <f>$D39*G$38</f>
         <v/>
       </c>
-      <c r="H39" s="54">
+      <c r="H39" s="52">
         <f>$D39*H$38</f>
         <v/>
       </c>
     </row>
-    <row r="40" ht="13.5" customHeight="1" s="158">
-      <c r="D40" s="47" t="n">
+    <row r="40" ht="13.5" customHeight="1">
+      <c r="D40" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="E40" s="39">
+      <c r="E40" s="38">
         <f>$D40*E$38</f>
         <v/>
       </c>
-      <c r="F40" s="56">
+      <c r="F40" s="53">
         <f>$D40*F$38</f>
         <v/>
       </c>
-      <c r="G40" s="56">
+      <c r="G40" s="53">
         <f>$D40*G$38</f>
         <v/>
       </c>
-      <c r="H40" s="56">
+      <c r="H40" s="53">
         <f>$D40*H$38</f>
         <v/>
       </c>
     </row>
-    <row r="41" ht="13.5" customHeight="1" s="158">
-      <c r="D41" s="47" t="n">
+    <row r="41" ht="13.5" customHeight="1">
+      <c r="D41" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E41" s="39">
+      <c r="E41" s="38">
         <f>$D41*E$38</f>
         <v/>
       </c>
-      <c r="F41" s="56">
+      <c r="F41" s="53">
         <f>$D41*F$38</f>
         <v/>
       </c>
-      <c r="G41" s="56">
+      <c r="G41" s="53">
         <f>$D41*G$38</f>
         <v/>
       </c>
-      <c r="H41" s="56">
+      <c r="H41" s="53">
         <f>$D41*H$38</f>
         <v/>
       </c>
     </row>
-    <row r="42" ht="13.5" customHeight="1" s="158">
-      <c r="D42" s="47" t="n">
+    <row r="42" ht="13.5" customHeight="1">
+      <c r="D42" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="E42" s="39">
+      <c r="E42" s="38">
         <f>$D42*E$38</f>
         <v/>
       </c>
-      <c r="F42" s="56">
+      <c r="F42" s="53">
         <f>$D42*F$38</f>
         <v/>
       </c>
-      <c r="G42" s="56">
+      <c r="G42" s="53">
         <f>$D42*G$38</f>
         <v/>
       </c>
-      <c r="H42" s="56">
+      <c r="H42" s="53">
         <f>$D42*H$38</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="13.5" customHeight="1" s="158">
-      <c r="D43" s="49" t="n">
+    <row r="43" ht="13.5" customHeight="1">
+      <c r="D43" s="48" t="n">
         <v>10</v>
       </c>
-      <c r="E43" s="41">
+      <c r="E43" s="40">
         <f>$D43*E$38</f>
         <v/>
       </c>
-      <c r="F43" s="58">
+      <c r="F43" s="54">
         <f>$D43*F$38</f>
         <v/>
       </c>
-      <c r="G43" s="58">
+      <c r="G43" s="54">
         <f>$D43*G$38</f>
         <v/>
       </c>
-      <c r="H43" s="58">
+      <c r="H43" s="54">
         <f>$D43*H$38</f>
         <v/>
       </c>

--- a/files/excel-mastery-1-2.xlsx
+++ b/files/excel-mastery-1-2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-1605" yWindow="-16320" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="280" windowWidth="17320" windowHeight="10400" tabRatio="773" firstSheet="2" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="1-2_操作イメージ" sheetId="1" state="visible" r:id="rId1"/>
@@ -553,7 +553,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1049,74 +1049,77 @@
     <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
